--- a/03_IO_Lists_and_Schedules/IO_List-By_SlotConfig.xlsx
+++ b/03_IO_Lists_and_Schedules/IO_List-By_SlotConfig.xlsx
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -6247,17 +6247,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL1-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C1S8-17/P1-TBRL1-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL1-17/C1S8-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -7115,17 +7115,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL1-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C1S8-35/P1-TBRL1-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL1-35/C1S8-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7135,22 +7135,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -8121,17 +8121,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL2-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C1S9-17/P1-TBRL2-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL2-17/C1S9-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -8997,17 +8997,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL2-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C1S9-35/P1-TBRL2-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P1-TBRL2-35/C1S9-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -9017,22 +9017,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -12941,7 +12941,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -13948,7 +13948,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -24539,7 +24539,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -25371,17 +25371,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL1-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S6-17/P2-TBRL1-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL1-17/C2S6-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -25391,22 +25391,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -26265,17 +26265,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL1-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S6-35/P2-TBRL1-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL1-35/C2S6-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -26285,22 +26285,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -26437,7 +26437,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -27255,17 +27255,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL2-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S7-17/P2-TBRL2-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL2-17/C2S7-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -27275,22 +27275,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -28125,17 +28125,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL2-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S7-35/P2-TBRL2-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL2-35/C2S7-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -28145,22 +28145,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -29129,17 +29129,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL3-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S8-17/P2-TBRL3-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL3-17/C2S8-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -29149,22 +29149,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -30029,17 +30029,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL3-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S8-35/P2-TBRL3-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBRL3-35/C2S8-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -30049,22 +30049,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -32115,7 +32115,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -33946,8 +33946,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -34051,17 +34051,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-1(B)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-1/P2-TBAI3-1(B)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-1(B)/C2S11-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -34071,22 +34071,22 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_1</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34101,17 +34101,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-2</t>
+          <t>P2-TBAI3-1(A)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C2S11-2/P2-TBAI3-2</t>
+          <t>C2S11-2/P2-TBAI3-1(A)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-2/C2S11-2</t>
+          <t>P2-TBAI3-1(A)/C2S11-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_2</t>
+          <t>Spare_AI_1</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -34151,17 +34151,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-2(B)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-3/P2-TBAI3-2(B)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-2(B)/C2S11-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_2</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34201,17 +34201,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-4</t>
+          <t>P2-TBAI3-2(A)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C2S11-4/P2-TBAI3-4</t>
+          <t>C2S11-4/P2-TBAI3-2(A)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-4/C2S11-4</t>
+          <t>P2-TBAI3-2(A)/C2S11-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_4</t>
+          <t>Spare_AI_2</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -34251,17 +34251,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-3(B)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-5/P2-TBAI3-3(B)</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-3(B)/C2S11-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -34271,22 +34271,22 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_3</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34301,17 +34301,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-6</t>
+          <t>P2-TBAI3-3(A)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C2S11-6/P2-TBAI3-6</t>
+          <t>C2S11-6/P2-TBAI3-3(A)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-6/C2S11-6</t>
+          <t>P2-TBAI3-3(A)/C2S11-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_6</t>
+          <t>Spare_AI_3</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -34351,17 +34351,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-4(B)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-7/P2-TBAI3-4(B)</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-4(B)/C2S11-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -34371,22 +34371,22 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_4</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34401,17 +34401,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-8</t>
+          <t>P2-TBAI3-4(A)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C2S11-8/P2-TBAI3-8</t>
+          <t>C2S11-8/P2-TBAI3-4(A)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-8/C2S11-8</t>
+          <t>P2-TBAI3-4(A)/C2S11-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_8</t>
+          <t>Spare_AI_4</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -34551,17 +34551,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-5(B)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-11/P2-TBAI3-5(B)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-5(B)/C2S11-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -34571,22 +34571,22 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_5</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34601,17 +34601,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-12</t>
+          <t>P2-TBAI3-5(A)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C2S11-12/P2-TBAI3-12</t>
+          <t>C2S11-12/P2-TBAI3-5(A)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-12/C2S11-12</t>
+          <t>P2-TBAI3-5(A)/C2S11-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_12</t>
+          <t>Spare_AI_5</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -34651,17 +34651,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-6(B)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-13/P2-TBAI3-6(B)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-6(B)/C2S11-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -34671,22 +34671,22 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_6</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34701,17 +34701,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-14</t>
+          <t>P2-TBAI3-6(A)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C2S11-14/P2-TBAI3-14</t>
+          <t>C2S11-14/P2-TBAI3-6(A)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-14/C2S11-14</t>
+          <t>P2-TBAI3-6(A)/C2S11-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -34721,7 +34721,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_14</t>
+          <t>Spare_AI_6</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -34751,17 +34751,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-7(B)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-15/P2-TBAI3-7(B)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-7(B)/C2S11-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -34771,22 +34771,22 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_7</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34801,17 +34801,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-16</t>
+          <t>P2-TBAI3-7(A)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C2S11-16/P2-TBAI3-16</t>
+          <t>C2S11-16/P2-TBAI3-7(A)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-16/C2S11-16</t>
+          <t>P2-TBAI3-7(A)/C2S11-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -34821,7 +34821,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_16</t>
+          <t>Spare_AI_7</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -34851,17 +34851,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-8(B)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-17/P2-TBAI3-8(B)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-8(B)/C2S11-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -34871,22 +34871,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_8</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -34901,17 +34901,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-18</t>
+          <t>P2-TBAI3-8(A)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>C2S11-18/P2-TBAI3-18</t>
+          <t>C2S11-18/P2-TBAI3-8(A)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-18/C2S11-18</t>
+          <t>P2-TBAI3-8(A)/C2S11-18</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_18</t>
+          <t>Spare_AI_8</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -34951,17 +34951,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-9(B)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-19/P2-TBAI3-9(B)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-9(B)/C2S11-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -34971,22 +34971,22 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_9</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35001,17 +35001,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-20</t>
+          <t>P2-TBAI3-9(A)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C2S11-20/P2-TBAI3-20</t>
+          <t>C2S11-20/P2-TBAI3-9(A)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-20/C2S11-20</t>
+          <t>P2-TBAI3-9(A)/C2S11-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_20</t>
+          <t>Spare_AI_9</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -35051,17 +35051,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-10(B)</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-21/P2-TBAI3-10(B)</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-10(B)/C2S11-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -35071,22 +35071,22 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_10</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35101,17 +35101,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-22</t>
+          <t>P2-TBAI3-10(A)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C2S11-22/P2-TBAI3-22</t>
+          <t>C2S11-22/P2-TBAI3-10(A)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-22/C2S11-22</t>
+          <t>P2-TBAI3-10(A)/C2S11-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -35121,7 +35121,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_22</t>
+          <t>Spare_AI_10</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -35151,17 +35151,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-11(B)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-23/P2-TBAI3-11(B)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-11(B)/C2S11-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -35171,22 +35171,22 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_11</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35201,17 +35201,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-24</t>
+          <t>P2-TBAI3-11(A)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C2S11-24/P2-TBAI3-24</t>
+          <t>C2S11-24/P2-TBAI3-11(A)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-24/C2S11-24</t>
+          <t>P2-TBAI3-11(A)/C2S11-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -35221,7 +35221,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_24</t>
+          <t>Spare_AI_11</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -35251,17 +35251,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-12(B)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-25/P2-TBAI3-12(B)</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-12(B)/C2S11-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -35271,22 +35271,22 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_12</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35301,17 +35301,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-26</t>
+          <t>P2-TBAI3-12(A)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C2S11-26/P2-TBAI3-26</t>
+          <t>C2S11-26/P2-TBAI3-12(A)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-26/C2S11-26</t>
+          <t>P2-TBAI3-12(A)/C2S11-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_26</t>
+          <t>Spare_AI_12</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -35451,17 +35451,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-13(B)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-29/P2-TBAI3-13(B)</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-13(B)/C2S11-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -35471,22 +35471,22 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_13</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35501,17 +35501,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-30</t>
+          <t>P2-TBAI3-13(A)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C2S11-30/P2-TBAI3-30</t>
+          <t>C2S11-30/P2-TBAI3-13(A)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-30/C2S11-30</t>
+          <t>P2-TBAI3-13(A)/C2S11-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_30</t>
+          <t>Spare_AI_13</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -35551,17 +35551,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-14(B)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-31/P2-TBAI3-14(B)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-14(B)/C2S11-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -35571,22 +35571,22 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_14</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35601,17 +35601,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-32</t>
+          <t>P2-TBAI3-14(A)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C2S11-32/P2-TBAI3-32</t>
+          <t>C2S11-32/P2-TBAI3-14(A)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-32/C2S11-32</t>
+          <t>P2-TBAI3-14(A)/C2S11-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_32</t>
+          <t>Spare_AI_14</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -35651,17 +35651,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-15(B)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-33/P2-TBAI3-15(B)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-15(B)/C2S11-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -35671,22 +35671,22 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_15</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35701,17 +35701,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-34</t>
+          <t>P2-TBAI3-15(A)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C2S11-34/P2-TBAI3-34</t>
+          <t>C2S11-34/P2-TBAI3-15(A)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-34/C2S11-34</t>
+          <t>P2-TBAI3-15(A)/C2S11-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_34</t>
+          <t>Spare_AI_15</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -35751,17 +35751,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-16(B)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S11-35/P2-TBAI3-16(B)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI3-16(B)/C2S11-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -35771,22 +35771,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_16</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -35801,17 +35801,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI3-36</t>
+          <t>P2-TBAI3-16(A)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>C2S11-36/P2-TBAI3-36</t>
+          <t>C2S11-36/P2-TBAI3-16(A)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI3-36/C2S11-36</t>
+          <t>P2-TBAI3-16(A)/C2S11-36</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_36</t>
+          <t>Spare_AI_16</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -35868,8 +35868,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -35923,7 +35923,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -35973,17 +35973,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-1(B)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-1/P2-TBAI4-1(B)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-1(B)/C2S12-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -35993,22 +35993,22 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_1</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36023,17 +36023,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-2</t>
+          <t>P2-TBAI4-1(A)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C2S12-2/P2-TBAI4-2</t>
+          <t>C2S12-2/P2-TBAI4-1(A)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-2/C2S12-2</t>
+          <t>P2-TBAI4-1(A)/C2S12-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_2</t>
+          <t>Spare_AI_1</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -36073,17 +36073,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-2(B)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-3/P2-TBAI4-2(B)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-2(B)/C2S12-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -36093,22 +36093,22 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_2</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36123,17 +36123,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-4</t>
+          <t>P2-TBAI4-2(A)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C2S12-4/P2-TBAI4-4</t>
+          <t>C2S12-4/P2-TBAI4-2(A)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-4/C2S12-4</t>
+          <t>P2-TBAI4-2(A)/C2S12-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -36143,7 +36143,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_4</t>
+          <t>Spare_AI_2</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -36173,17 +36173,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-3(B)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-5/P2-TBAI4-3(B)</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-3(B)/C2S12-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -36193,22 +36193,22 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_3</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36223,17 +36223,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-6</t>
+          <t>P2-TBAI4-3(A)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C2S12-6/P2-TBAI4-6</t>
+          <t>C2S12-6/P2-TBAI4-3(A)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-6/C2S12-6</t>
+          <t>P2-TBAI4-3(A)/C2S12-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_6</t>
+          <t>Spare_AI_3</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -36273,17 +36273,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-4(B)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-7/P2-TBAI4-4(B)</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-4(B)/C2S12-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -36293,22 +36293,22 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_4</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36323,17 +36323,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-8</t>
+          <t>P2-TBAI4-4(A)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C2S12-8/P2-TBAI4-8</t>
+          <t>C2S12-8/P2-TBAI4-4(A)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-8/C2S12-8</t>
+          <t>P2-TBAI4-4(A)/C2S12-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -36343,7 +36343,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_8</t>
+          <t>Spare_AI_4</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -36473,17 +36473,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-5(B)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-11/P2-TBAI4-5(B)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-5(B)/C2S12-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -36493,22 +36493,22 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_5</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36523,17 +36523,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-12</t>
+          <t>P2-TBAI4-5(A)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C2S12-12/P2-TBAI4-12</t>
+          <t>C2S12-12/P2-TBAI4-5(A)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-12/C2S12-12</t>
+          <t>P2-TBAI4-5(A)/C2S12-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_12</t>
+          <t>Spare_AI_5</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -36573,17 +36573,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-6(B)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-13/P2-TBAI4-6(B)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-6(B)/C2S12-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -36593,22 +36593,22 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_6</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36623,17 +36623,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-14</t>
+          <t>P2-TBAI4-6(A)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C2S12-14/P2-TBAI4-14</t>
+          <t>C2S12-14/P2-TBAI4-6(A)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-14/C2S12-14</t>
+          <t>P2-TBAI4-6(A)/C2S12-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -36643,7 +36643,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_14</t>
+          <t>Spare_AI_6</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -36673,17 +36673,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-7(B)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-15/P2-TBAI4-7(B)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-7(B)/C2S12-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -36693,22 +36693,22 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_7</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36723,17 +36723,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-16</t>
+          <t>P2-TBAI4-7(A)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C2S12-16/P2-TBAI4-16</t>
+          <t>C2S12-16/P2-TBAI4-7(A)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-16/C2S12-16</t>
+          <t>P2-TBAI4-7(A)/C2S12-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_16</t>
+          <t>Spare_AI_7</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -36773,17 +36773,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-8(B)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-17/P2-TBAI4-8(B)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-8(B)/C2S12-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -36793,22 +36793,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_8</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36823,17 +36823,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-18</t>
+          <t>P2-TBAI4-8(A)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>C2S12-18/P2-TBAI4-18</t>
+          <t>C2S12-18/P2-TBAI4-8(A)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-18/C2S12-18</t>
+          <t>P2-TBAI4-8(A)/C2S12-18</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -36843,7 +36843,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_18</t>
+          <t>Spare_AI_8</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -36873,17 +36873,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-9(B)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-19/P2-TBAI4-9(B)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-9(B)/C2S12-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -36893,22 +36893,22 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_9</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -36923,17 +36923,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-20</t>
+          <t>P2-TBAI4-9(A)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C2S12-20/P2-TBAI4-20</t>
+          <t>C2S12-20/P2-TBAI4-9(A)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-20/C2S12-20</t>
+          <t>P2-TBAI4-9(A)/C2S12-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_20</t>
+          <t>Spare_AI_9</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -36973,17 +36973,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-10(B)</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-21/P2-TBAI4-10(B)</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-10(B)/C2S12-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -36993,22 +36993,22 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_10</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37023,17 +37023,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-22</t>
+          <t>P2-TBAI4-10(A)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C2S12-22/P2-TBAI4-22</t>
+          <t>C2S12-22/P2-TBAI4-10(A)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-22/C2S12-22</t>
+          <t>P2-TBAI4-10(A)/C2S12-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -37043,7 +37043,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_22</t>
+          <t>Spare_AI_10</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -37073,17 +37073,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-11(B)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-23/P2-TBAI4-11(B)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-11(B)/C2S12-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -37093,22 +37093,22 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_11</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37123,17 +37123,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-24</t>
+          <t>P2-TBAI4-11(A)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C2S12-24/P2-TBAI4-24</t>
+          <t>C2S12-24/P2-TBAI4-11(A)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-24/C2S12-24</t>
+          <t>P2-TBAI4-11(A)/C2S12-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -37143,7 +37143,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_24</t>
+          <t>Spare_AI_11</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -37173,17 +37173,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-12(B)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-25/P2-TBAI4-12(B)</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-12(B)/C2S12-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -37193,22 +37193,22 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_12</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37223,17 +37223,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-26</t>
+          <t>P2-TBAI4-12(A)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C2S12-26/P2-TBAI4-26</t>
+          <t>C2S12-26/P2-TBAI4-12(A)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-26/C2S12-26</t>
+          <t>P2-TBAI4-12(A)/C2S12-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -37243,7 +37243,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_26</t>
+          <t>Spare_AI_12</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -37373,17 +37373,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-13(B)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-29/P2-TBAI4-13(B)</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-13(B)/C2S12-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -37393,22 +37393,22 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_13</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37423,17 +37423,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-30</t>
+          <t>P2-TBAI4-13(A)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C2S12-30/P2-TBAI4-30</t>
+          <t>C2S12-30/P2-TBAI4-13(A)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-30/C2S12-30</t>
+          <t>P2-TBAI4-13(A)/C2S12-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -37443,7 +37443,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_30</t>
+          <t>Spare_AI_13</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -37473,17 +37473,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-14(B)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-31/P2-TBAI4-14(B)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-14(B)/C2S12-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -37493,22 +37493,22 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_14</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37523,17 +37523,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-32</t>
+          <t>P2-TBAI4-14(A)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C2S12-32/P2-TBAI4-32</t>
+          <t>C2S12-32/P2-TBAI4-14(A)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-32/C2S12-32</t>
+          <t>P2-TBAI4-14(A)/C2S12-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -37543,7 +37543,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_32</t>
+          <t>Spare_AI_14</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -37573,17 +37573,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-15(B)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-33/P2-TBAI4-15(B)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-15(B)/C2S12-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -37593,22 +37593,22 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_15</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37623,17 +37623,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-34</t>
+          <t>P2-TBAI4-15(A)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C2S12-34/P2-TBAI4-34</t>
+          <t>C2S12-34/P2-TBAI4-15(A)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-34/C2S12-34</t>
+          <t>P2-TBAI4-15(A)/C2S12-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -37643,7 +37643,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_34</t>
+          <t>Spare_AI_15</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -37673,17 +37673,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-16(B)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C2S12-35/P2-TBAI4-16(B)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P2-TBAI4-16(B)/C2S12-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -37693,22 +37693,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_AI_16</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -37723,17 +37723,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>P2-TBAI4-36</t>
+          <t>P2-TBAI4-16(A)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>C2S12-36/P2-TBAI4-36</t>
+          <t>C2S12-36/P2-TBAI4-16(A)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>P2-TBAI4-36/C2S12-36</t>
+          <t>P2-TBAI4-16(A)/C2S12-36</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -37743,7 +37743,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Spare_AI_36</t>
+          <t>Spare_AI_16</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -37789,7 +37789,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="82" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
@@ -37845,7 +37845,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -39010,7 +39010,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -39066,7 +39066,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -45096,7 +45096,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -45944,17 +45944,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL1-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C3S4-17/P3-TBRL1-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL1-17/C3S4-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -45964,22 +45964,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -46814,17 +46814,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL1-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C3S4-35/P3-TBRL1-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL1-35/C3S4-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -46834,22 +46834,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -46986,7 +46986,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -47818,17 +47818,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL2-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C3S5-17/P3-TBRL2-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL2-17/C3S5-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -47838,22 +47838,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -48718,17 +48718,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL2-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C3S5-35/P3-TBRL2-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P3-TBRL2-35/C3S5-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -48738,22 +48738,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -48890,7 +48890,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -50756,7 +50756,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -52614,7 +52614,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -54448,7 +54448,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -54504,7 +54504,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -54834,7 +54834,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -56688,7 +56688,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -56744,7 +56744,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -56862,7 +56862,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -56918,7 +56918,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -57092,7 +57092,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAOx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -57172,7 +57172,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
@@ -57222,7 +57222,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
@@ -57472,7 +57472,7 @@
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
@@ -57522,7 +57522,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
@@ -57672,7 +57672,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -57722,7 +57722,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
@@ -57972,7 +57972,7 @@
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
@@ -58022,7 +58022,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
+          <t>Loop Power Terminal (+24VDC)</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -59019,7 +59019,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -59075,7 +59075,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -65071,7 +65071,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -65919,17 +65919,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P4-TBRL1-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C4S4-17/P4-TBRL1-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P4-TBRL1-17/C4S4-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -65939,22 +65939,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -66819,17 +66819,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P4-TBRL1-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C4S4-35/P4-TBRL1-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P4-TBRL1-35/C4S4-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -66839,22 +66839,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -66935,7 +66935,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -66991,7 +66991,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -67321,7 +67321,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -69203,7 +69203,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71057,7 +71057,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71113,7 +71113,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71231,7 +71231,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71287,7 +71287,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71405,7 +71405,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71461,7 +71461,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71579,7 +71579,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71635,7 +71635,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71753,7 +71753,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71809,7 +71809,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -71927,7 +71927,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -71983,7 +71983,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -72528,7 +72528,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -72584,7 +72584,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -72858,7 +72858,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -72914,7 +72914,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -73189,8 +73189,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -73294,17 +73294,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>P5-TBDI1-1</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>C5S1-1/-1</t>
+          <t>C5S1-1/P5-TBDI1-1</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>-1/C5S1-1</t>
+          <t>P5-TBDI1-1/C5S1-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -73342,17 +73342,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>P5-TBDI1-2</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C5S1-2/-2</t>
+          <t>C5S1-2/P5-TBDI1-2</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-2/C5S1-2</t>
+          <t>P5-TBDI1-2/C5S1-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -73390,17 +73390,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>P5-TBDI1-3</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>C5S1-3/-3</t>
+          <t>C5S1-3/P5-TBDI1-3</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>-3/C5S1-3</t>
+          <t>P5-TBDI1-3/C5S1-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -73438,17 +73438,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>P5-TBDI1-4</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C5S1-4/-4</t>
+          <t>C5S1-4/P5-TBDI1-4</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-4/C5S1-4</t>
+          <t>P5-TBDI1-4/C5S1-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -73486,17 +73486,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>P5-TBDI1-5</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>C5S1-5/-5</t>
+          <t>C5S1-5/P5-TBDI1-5</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>-5/C5S1-5</t>
+          <t>P5-TBDI1-5/C5S1-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -73534,17 +73534,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>P5-TBDI1-6</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C5S1-6/-6</t>
+          <t>C5S1-6/P5-TBDI1-6</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>-6/C5S1-6</t>
+          <t>P5-TBDI1-6/C5S1-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -73582,17 +73582,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>P5-TBDI1-7</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>C5S1-7/-7</t>
+          <t>C5S1-7/P5-TBDI1-7</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>-7/C5S1-7</t>
+          <t>P5-TBDI1-7/C5S1-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -73630,17 +73630,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>P5-TBDI1-8</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C5S1-8/-8</t>
+          <t>C5S1-8/P5-TBDI1-8</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-8/C5S1-8</t>
+          <t>P5-TBDI1-8/C5S1-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -73680,17 +73680,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>P5-TBDI1-9</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>C5S1-9/-9</t>
+          <t>C5S1-9/P5-TBDI1-9</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>-9/C5S1-9</t>
+          <t>P5-TBDI1-9/C5S1-9</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -73730,17 +73730,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>P5-TBDI1-10</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>C5S1-10/-10</t>
+          <t>C5S1-10/P5-TBDI1-10</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>-10/C5S1-10</t>
+          <t>P5-TBDI1-10/C5S1-10</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -73780,17 +73780,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>P5-TBDI1-11</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>C5S1-11/-11</t>
+          <t>C5S1-11/P5-TBDI1-11</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>-11/C5S1-11</t>
+          <t>P5-TBDI1-11/C5S1-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -73830,17 +73830,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>P5-TBDI1-12</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C5S1-12/-12</t>
+          <t>C5S1-12/P5-TBDI1-12</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-12/C5S1-12</t>
+          <t>P5-TBDI1-12/C5S1-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -73880,17 +73880,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>P5-TBDI1-13</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>C5S1-13/-13</t>
+          <t>C5S1-13/P5-TBDI1-13</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>-13/C5S1-13</t>
+          <t>P5-TBDI1-13/C5S1-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -73930,17 +73930,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>P5-TBDI1-14</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C5S1-14/-14</t>
+          <t>C5S1-14/P5-TBDI1-14</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>-14/C5S1-14</t>
+          <t>P5-TBDI1-14/C5S1-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -73980,17 +73980,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>P5-TBDI1-15</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>C5S1-15/-15</t>
+          <t>C5S1-15/P5-TBDI1-15</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>-15/C5S1-15</t>
+          <t>P5-TBDI1-15/C5S1-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -74028,17 +74028,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>P5-TBDI1-16</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C5S1-16/-16</t>
+          <t>C5S1-16/P5-TBDI1-16</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-16/C5S1-16</t>
+          <t>P5-TBDI1-16/C5S1-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -74176,17 +74176,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>P5-TBDI1-17</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>C5S1-19/-17</t>
+          <t>C5S1-19/P5-TBDI1-17</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>-17/C5S1-19</t>
+          <t>P5-TBDI1-17/C5S1-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -74224,17 +74224,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>P5-TBDI1-18</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C5S1-20/-18</t>
+          <t>C5S1-20/P5-TBDI1-18</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>-18/C5S1-20</t>
+          <t>P5-TBDI1-18/C5S1-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -74272,17 +74272,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>P5-TBDI1-19</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>C5S1-21/-19</t>
+          <t>C5S1-21/P5-TBDI1-19</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>-19/C5S1-21</t>
+          <t>P5-TBDI1-19/C5S1-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -74320,17 +74320,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>P5-TBDI1-20</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C5S1-22/-20</t>
+          <t>C5S1-22/P5-TBDI1-20</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-20/C5S1-22</t>
+          <t>P5-TBDI1-20/C5S1-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -74368,17 +74368,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>P5-TBDI1-21</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>C5S1-23/-21</t>
+          <t>C5S1-23/P5-TBDI1-21</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-21/C5S1-23</t>
+          <t>P5-TBDI1-21/C5S1-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -74416,17 +74416,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>P5-TBDI1-22</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C5S1-24/-22</t>
+          <t>C5S1-24/P5-TBDI1-22</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-22/C5S1-24</t>
+          <t>P5-TBDI1-22/C5S1-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -74464,17 +74464,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>P5-TBDI1-23</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>C5S1-25/-23</t>
+          <t>C5S1-25/P5-TBDI1-23</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>-23/C5S1-25</t>
+          <t>P5-TBDI1-23/C5S1-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -74512,17 +74512,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>P5-TBDI1-24</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C5S1-26/-24</t>
+          <t>C5S1-26/P5-TBDI1-24</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-24/C5S1-26</t>
+          <t>P5-TBDI1-24/C5S1-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -74560,17 +74560,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>P5-TBDI1-25</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>C5S1-27/-25</t>
+          <t>C5S1-27/P5-TBDI1-25</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>-25/C5S1-27</t>
+          <t>P5-TBDI1-25/C5S1-27</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -74608,17 +74608,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>P5-TBDI1-26</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>C5S1-28/-26</t>
+          <t>C5S1-28/P5-TBDI1-26</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>-26/C5S1-28</t>
+          <t>P5-TBDI1-26/C5S1-28</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -74656,17 +74656,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>P5-TBDI1-27</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>C5S1-29/-27</t>
+          <t>C5S1-29/P5-TBDI1-27</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>-27/C5S1-29</t>
+          <t>P5-TBDI1-27/C5S1-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -74704,17 +74704,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>P5-TBDI1-28</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C5S1-30/-28</t>
+          <t>C5S1-30/P5-TBDI1-28</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-28/C5S1-30</t>
+          <t>P5-TBDI1-28/C5S1-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -74752,17 +74752,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>P5-TBDI1-29</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>C5S1-31/-29</t>
+          <t>C5S1-31/P5-TBDI1-29</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>-29/C5S1-31</t>
+          <t>P5-TBDI1-29/C5S1-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -74800,17 +74800,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>P5-TBDI1-30</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C5S1-32/-30</t>
+          <t>C5S1-32/P5-TBDI1-30</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-30/C5S1-32</t>
+          <t>P5-TBDI1-30/C5S1-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -74848,17 +74848,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>P5-TBDI1-31</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>C5S1-33/-31</t>
+          <t>C5S1-33/P5-TBDI1-31</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>-31/C5S1-33</t>
+          <t>P5-TBDI1-31/C5S1-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -74896,17 +74896,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>P5-TBDI1-32</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C5S1-34/-32</t>
+          <t>C5S1-34/P5-TBDI1-32</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>-32/C5S1-34</t>
+          <t>P5-TBDI1-32/C5S1-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -75061,8 +75061,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -75166,17 +75166,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>P5-TBDI2-1</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>C5S2-1/-1</t>
+          <t>C5S2-1/P5-TBDI2-1</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>-1/C5S2-1</t>
+          <t>P5-TBDI2-1/C5S2-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -75214,17 +75214,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>P5-TBDI2-2</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C5S2-2/-2</t>
+          <t>C5S2-2/P5-TBDI2-2</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-2/C5S2-2</t>
+          <t>P5-TBDI2-2/C5S2-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -75262,17 +75262,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>P5-TBDI2-3</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>C5S2-3/-3</t>
+          <t>C5S2-3/P5-TBDI2-3</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>-3/C5S2-3</t>
+          <t>P5-TBDI2-3/C5S2-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -75310,17 +75310,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>P5-TBDI2-4</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C5S2-4/-4</t>
+          <t>C5S2-4/P5-TBDI2-4</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-4/C5S2-4</t>
+          <t>P5-TBDI2-4/C5S2-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -75358,17 +75358,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>P5-TBDI2-5</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>C5S2-5/-5</t>
+          <t>C5S2-5/P5-TBDI2-5</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>-5/C5S2-5</t>
+          <t>P5-TBDI2-5/C5S2-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -75406,17 +75406,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>P5-TBDI2-6</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C5S2-6/-6</t>
+          <t>C5S2-6/P5-TBDI2-6</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>-6/C5S2-6</t>
+          <t>P5-TBDI2-6/C5S2-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -75454,17 +75454,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>P5-TBDI2-7</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>C5S2-7/-7</t>
+          <t>C5S2-7/P5-TBDI2-7</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>-7/C5S2-7</t>
+          <t>P5-TBDI2-7/C5S2-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -75502,17 +75502,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>P5-TBDI2-8</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C5S2-8/-8</t>
+          <t>C5S2-8/P5-TBDI2-8</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-8/C5S2-8</t>
+          <t>P5-TBDI2-8/C5S2-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -75550,17 +75550,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>P5-TBDI2-9</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>C5S2-9/-9</t>
+          <t>C5S2-9/P5-TBDI2-9</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>-9/C5S2-9</t>
+          <t>P5-TBDI2-9/C5S2-9</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -75600,17 +75600,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>P5-TBDI2-10</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>C5S2-10/-10</t>
+          <t>C5S2-10/P5-TBDI2-10</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>-10/C5S2-10</t>
+          <t>P5-TBDI2-10/C5S2-10</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -75650,17 +75650,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>P5-TBDI2-11</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>C5S2-11/-11</t>
+          <t>C5S2-11/P5-TBDI2-11</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>-11/C5S2-11</t>
+          <t>P5-TBDI2-11/C5S2-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -75700,17 +75700,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>P5-TBDI2-12</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C5S2-12/-12</t>
+          <t>C5S2-12/P5-TBDI2-12</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-12/C5S2-12</t>
+          <t>P5-TBDI2-12/C5S2-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -75750,17 +75750,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>P5-TBDI2-13</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>C5S2-13/-13</t>
+          <t>C5S2-13/P5-TBDI2-13</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>-13/C5S2-13</t>
+          <t>P5-TBDI2-13/C5S2-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -75800,17 +75800,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>P5-TBDI2-14</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C5S2-14/-14</t>
+          <t>C5S2-14/P5-TBDI2-14</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>-14/C5S2-14</t>
+          <t>P5-TBDI2-14/C5S2-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -75850,17 +75850,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>P5-TBDI2-15</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>C5S2-15/-15</t>
+          <t>C5S2-15/P5-TBDI2-15</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>-15/C5S2-15</t>
+          <t>P5-TBDI2-15/C5S2-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -75900,17 +75900,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>P5-TBDI2-16</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C5S2-16/-16</t>
+          <t>C5S2-16/P5-TBDI2-16</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-16/C5S2-16</t>
+          <t>P5-TBDI2-16/C5S2-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -76050,17 +76050,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>P5-TBDI2-17</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>C5S2-19/-17</t>
+          <t>C5S2-19/P5-TBDI2-17</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>-17/C5S2-19</t>
+          <t>P5-TBDI2-17/C5S2-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -76100,17 +76100,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>P5-TBDI2-18</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C5S2-20/-18</t>
+          <t>C5S2-20/P5-TBDI2-18</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>-18/C5S2-20</t>
+          <t>P5-TBDI2-18/C5S2-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -76150,17 +76150,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>P5-TBDI2-19</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>C5S2-21/-19</t>
+          <t>C5S2-21/P5-TBDI2-19</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>-19/C5S2-21</t>
+          <t>P5-TBDI2-19/C5S2-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -76200,17 +76200,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>P5-TBDI2-20</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C5S2-22/-20</t>
+          <t>C5S2-22/P5-TBDI2-20</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-20/C5S2-22</t>
+          <t>P5-TBDI2-20/C5S2-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -76250,17 +76250,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>P5-TBDI2-21</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>C5S2-23/-21</t>
+          <t>C5S2-23/P5-TBDI2-21</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-21/C5S2-23</t>
+          <t>P5-TBDI2-21/C5S2-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -76300,17 +76300,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>P5-TBDI2-22</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C5S2-24/-22</t>
+          <t>C5S2-24/P5-TBDI2-22</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-22/C5S2-24</t>
+          <t>P5-TBDI2-22/C5S2-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -76350,17 +76350,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>P5-TBDI2-23</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>C5S2-25/-23</t>
+          <t>C5S2-25/P5-TBDI2-23</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>-23/C5S2-25</t>
+          <t>P5-TBDI2-23/C5S2-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -76400,17 +76400,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>P5-TBDI2-24</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C5S2-26/-24</t>
+          <t>C5S2-26/P5-TBDI2-24</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-24/C5S2-26</t>
+          <t>P5-TBDI2-24/C5S2-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -76450,17 +76450,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>P5-TBDI2-25</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>C5S2-27/-25</t>
+          <t>C5S2-27/P5-TBDI2-25</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>-25/C5S2-27</t>
+          <t>P5-TBDI2-25/C5S2-27</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -76500,17 +76500,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>P5-TBDI2-26</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>C5S2-28/-26</t>
+          <t>C5S2-28/P5-TBDI2-26</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>-26/C5S2-28</t>
+          <t>P5-TBDI2-26/C5S2-28</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -76550,17 +76550,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>P5-TBDI2-27</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>C5S2-29/-27</t>
+          <t>C5S2-29/P5-TBDI2-27</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>-27/C5S2-29</t>
+          <t>P5-TBDI2-27/C5S2-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -76600,17 +76600,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>P5-TBDI2-28</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C5S2-30/-28</t>
+          <t>C5S2-30/P5-TBDI2-28</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-28/C5S2-30</t>
+          <t>P5-TBDI2-28/C5S2-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -76650,17 +76650,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>P5-TBDI2-29</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>C5S2-31/-29</t>
+          <t>C5S2-31/P5-TBDI2-29</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>-29/C5S2-31</t>
+          <t>P5-TBDI2-29/C5S2-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -76700,17 +76700,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>P5-TBDI2-30</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C5S2-32/-30</t>
+          <t>C5S2-32/P5-TBDI2-30</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-30/C5S2-32</t>
+          <t>P5-TBDI2-30/C5S2-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -76750,17 +76750,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>P5-TBDI2-31</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>C5S2-33/-31</t>
+          <t>C5S2-33/P5-TBDI2-31</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>-31/C5S2-33</t>
+          <t>P5-TBDI2-31/C5S2-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -76800,17 +76800,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>P5-TBDI2-32</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C5S2-34/-32</t>
+          <t>C5S2-34/P5-TBDI2-32</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>-32/C5S2-34</t>
+          <t>P5-TBDI2-32/C5S2-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -76967,8 +76967,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -77022,7 +77022,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBRLx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -77072,17 +77072,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>P5-TBRL1-1</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>C5S3-1/-1</t>
+          <t>C5S3-1/P5-TBRL1-1</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>-1/C5S3-1</t>
+          <t>P5-TBRL1-1/C5S3-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -77120,17 +77120,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>P5-TBRL1-2</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C5S3-2/-2</t>
+          <t>C5S3-2/P5-TBRL1-2</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-2/C5S3-2</t>
+          <t>P5-TBRL1-2/C5S3-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -77168,17 +77168,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>P5-TBRL1-3</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>C5S3-3/-3</t>
+          <t>C5S3-3/P5-TBRL1-3</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>-3/C5S3-3</t>
+          <t>P5-TBRL1-3/C5S3-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -77216,17 +77216,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>P5-TBRL1-4</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C5S3-4/-4</t>
+          <t>C5S3-4/P5-TBRL1-4</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-4/C5S3-4</t>
+          <t>P5-TBRL1-4/C5S3-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -77264,17 +77264,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>P5-TBRL1-5</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>C5S3-5/-5</t>
+          <t>C5S3-5/P5-TBRL1-5</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>-5/C5S3-5</t>
+          <t>P5-TBRL1-5/C5S3-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -77312,17 +77312,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>P5-TBRL1-6</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C5S3-6/-6</t>
+          <t>C5S3-6/P5-TBRL1-6</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>-6/C5S3-6</t>
+          <t>P5-TBRL1-6/C5S3-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -77360,17 +77360,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>P5-TBRL1-7</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>C5S3-7/-7</t>
+          <t>C5S3-7/P5-TBRL1-7</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>-7/C5S3-7</t>
+          <t>P5-TBRL1-7/C5S3-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -77408,17 +77408,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>P5-TBRL1-8</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C5S3-8/-8</t>
+          <t>C5S3-8/P5-TBRL1-8</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-8/C5S3-8</t>
+          <t>P5-TBRL1-8/C5S3-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -77456,17 +77456,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>P5-TBRL1-9</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>C5S3-9/-9</t>
+          <t>C5S3-9/P5-TBRL1-9</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>-9/C5S3-9</t>
+          <t>P5-TBRL1-9/C5S3-9</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -77506,17 +77506,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>P5-TBRL1-10</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>C5S3-10/-10</t>
+          <t>C5S3-10/P5-TBRL1-10</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>-10/C5S3-10</t>
+          <t>P5-TBRL1-10/C5S3-10</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -77556,17 +77556,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>P5-TBRL1-11</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>C5S3-11/-11</t>
+          <t>C5S3-11/P5-TBRL1-11</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>-11/C5S3-11</t>
+          <t>P5-TBRL1-11/C5S3-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -77606,17 +77606,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>P5-TBRL1-12</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C5S3-12/-12</t>
+          <t>C5S3-12/P5-TBRL1-12</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-12/C5S3-12</t>
+          <t>P5-TBRL1-12/C5S3-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -77656,17 +77656,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>P5-TBRL1-13</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>C5S3-13/-13</t>
+          <t>C5S3-13/P5-TBRL1-13</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>-13/C5S3-13</t>
+          <t>P5-TBRL1-13/C5S3-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -77706,17 +77706,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>P5-TBRL1-14</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C5S3-14/-14</t>
+          <t>C5S3-14/P5-TBRL1-14</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>-14/C5S3-14</t>
+          <t>P5-TBRL1-14/C5S3-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -77756,17 +77756,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>P5-TBRL1-15</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>C5S3-15/-15</t>
+          <t>C5S3-15/P5-TBRL1-15</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>-15/C5S3-15</t>
+          <t>P5-TBRL1-15/C5S3-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -77806,17 +77806,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>P5-TBRL1-16</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C5S3-16/-16</t>
+          <t>C5S3-16/P5-TBRL1-16</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-16/C5S3-16</t>
+          <t>P5-TBRL1-16/C5S3-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -77856,17 +77856,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P5-TBRL1-17</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C5S3-17/P5-TBRL1-17</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P5-TBRL1-17/C5S3-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -77876,22 +77876,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_17</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -77956,17 +77956,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>P5-TBRL1-17</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>C5S3-19/-17</t>
+          <t>C5S3-19/P5-TBRL1-17</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>-17/C5S3-19</t>
+          <t>P5-TBRL1-17/C5S3-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -78006,17 +78006,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>P5-TBRL1-18</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C5S3-20/-18</t>
+          <t>C5S3-20/P5-TBRL1-18</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>-18/C5S3-20</t>
+          <t>P5-TBRL1-18/C5S3-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -78056,17 +78056,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>P5-TBRL1-19</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>C5S3-21/-19</t>
+          <t>C5S3-21/P5-TBRL1-19</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>-19/C5S3-21</t>
+          <t>P5-TBRL1-19/C5S3-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -78106,17 +78106,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>P5-TBRL1-20</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C5S3-22/-20</t>
+          <t>C5S3-22/P5-TBRL1-20</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-20/C5S3-22</t>
+          <t>P5-TBRL1-20/C5S3-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -78156,17 +78156,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>P5-TBRL1-21</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>C5S3-23/-21</t>
+          <t>C5S3-23/P5-TBRL1-21</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-21/C5S3-23</t>
+          <t>P5-TBRL1-21/C5S3-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -78206,17 +78206,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>P5-TBRL1-22</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C5S3-24/-22</t>
+          <t>C5S3-24/P5-TBRL1-22</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-22/C5S3-24</t>
+          <t>P5-TBRL1-22/C5S3-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -78256,17 +78256,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>P5-TBRL1-23</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>C5S3-25/-23</t>
+          <t>C5S3-25/P5-TBRL1-23</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>-23/C5S3-25</t>
+          <t>P5-TBRL1-23/C5S3-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -78306,17 +78306,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>P5-TBRL1-24</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C5S3-26/-24</t>
+          <t>C5S3-26/P5-TBRL1-24</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-24/C5S3-26</t>
+          <t>P5-TBRL1-24/C5S3-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -78356,17 +78356,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>P5-TBRL1-25</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>C5S3-27/-25</t>
+          <t>C5S3-27/P5-TBRL1-25</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>-25/C5S3-27</t>
+          <t>P5-TBRL1-25/C5S3-27</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -78406,17 +78406,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>P5-TBRL1-26</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>C5S3-28/-26</t>
+          <t>C5S3-28/P5-TBRL1-26</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>-26/C5S3-28</t>
+          <t>P5-TBRL1-26/C5S3-28</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -78456,17 +78456,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>P5-TBRL1-27</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>C5S3-29/-27</t>
+          <t>C5S3-29/P5-TBRL1-27</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>-27/C5S3-29</t>
+          <t>P5-TBRL1-27/C5S3-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -78506,17 +78506,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>P5-TBRL1-28</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C5S3-30/-28</t>
+          <t>C5S3-30/P5-TBRL1-28</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-28/C5S3-30</t>
+          <t>P5-TBRL1-28/C5S3-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -78556,17 +78556,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>P5-TBRL1-29</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>C5S3-31/-29</t>
+          <t>C5S3-31/P5-TBRL1-29</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>-29/C5S3-31</t>
+          <t>P5-TBRL1-29/C5S3-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -78606,17 +78606,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>P5-TBRL1-30</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C5S3-32/-30</t>
+          <t>C5S3-32/P5-TBRL1-30</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-30/C5S3-32</t>
+          <t>P5-TBRL1-30/C5S3-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -78656,17 +78656,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>P5-TBRL1-31</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>C5S3-33/-31</t>
+          <t>C5S3-33/P5-TBRL1-31</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>-31/C5S3-33</t>
+          <t>P5-TBRL1-31/C5S3-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -78706,17 +78706,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>P5-TBRL1-32</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C5S3-34/-32</t>
+          <t>C5S3-34/P5-TBRL1-32</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>-32/C5S3-34</t>
+          <t>P5-TBRL1-32/C5S3-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -78756,17 +78756,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P5-TBRL1-35</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>C5S3-35/P5-TBRL1-35</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>0VDC</t>
+          <t>P5-TBRL1-35/C5S3-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -78776,22 +78776,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Internal Power Common</t>
+          <t>Spare_DO_35</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Module Power / Common Return Terminal</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>COMMON</t>
+          <t>Spare Reserve Channel</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>
@@ -78873,8 +78873,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -78928,7 +78928,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Terminal_Number (Px-TBDIx-m)</t>
+          <t>Terminal_Number (Px-TBAIx-m)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -78978,17 +78978,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>-1(B)</t>
+          <t>P5-TBAI1-1(B)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>C5S4-1/-1(B)</t>
+          <t>C5S4-1/P5-TBAI1-1(B)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>-1(B)/C5S4-1</t>
+          <t>P5-TBAI1-1(B)/C5S4-1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -79026,17 +79026,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>-1(A)</t>
+          <t>P5-TBAI1-1(A)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>C5S4-2/-1(A)</t>
+          <t>C5S4-2/P5-TBAI1-1(A)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-1(A)/C5S4-2</t>
+          <t>P5-TBAI1-1(A)/C5S4-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -79074,17 +79074,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>-2(B)</t>
+          <t>P5-TBAI1-2(B)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>C5S4-3/-2(B)</t>
+          <t>C5S4-3/P5-TBAI1-2(B)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>-2(B)/C5S4-3</t>
+          <t>P5-TBAI1-2(B)/C5S4-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -79122,17 +79122,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>-2(A)</t>
+          <t>P5-TBAI1-2(A)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C5S4-4/-2(A)</t>
+          <t>C5S4-4/P5-TBAI1-2(A)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-2(A)/C5S4-4</t>
+          <t>P5-TBAI1-2(A)/C5S4-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -79170,17 +79170,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>-3(B)</t>
+          <t>P5-TBAI1-3(B)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>C5S4-5/-3(B)</t>
+          <t>C5S4-5/P5-TBAI1-3(B)</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>-3(B)/C5S4-5</t>
+          <t>P5-TBAI1-3(B)/C5S4-5</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -79218,17 +79218,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>-3(A)</t>
+          <t>P5-TBAI1-3(A)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C5S4-6/-3(A)</t>
+          <t>C5S4-6/P5-TBAI1-3(A)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>-3(A)/C5S4-6</t>
+          <t>P5-TBAI1-3(A)/C5S4-6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -79266,17 +79266,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>-4(B)</t>
+          <t>P5-TBAI1-4(B)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>C5S4-7/-4(B)</t>
+          <t>C5S4-7/P5-TBAI1-4(B)</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>-4(B)/C5S4-7</t>
+          <t>P5-TBAI1-4(B)/C5S4-7</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -79314,17 +79314,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>-4(A)</t>
+          <t>P5-TBAI1-4(A)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C5S4-8/-4(A)</t>
+          <t>C5S4-8/P5-TBAI1-4(A)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-4(A)/C5S4-8</t>
+          <t>P5-TBAI1-4(A)/C5S4-8</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -79462,17 +79462,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>-5(B)</t>
+          <t>P5-TBAI1-5(B)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>C5S4-11/-5(B)</t>
+          <t>C5S4-11/P5-TBAI1-5(B)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>-5(B)/C5S4-11</t>
+          <t>P5-TBAI1-5(B)/C5S4-11</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -79510,17 +79510,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>-5(A)</t>
+          <t>P5-TBAI1-5(A)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C5S4-12/-5(A)</t>
+          <t>C5S4-12/P5-TBAI1-5(A)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-5(A)/C5S4-12</t>
+          <t>P5-TBAI1-5(A)/C5S4-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -79558,17 +79558,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>-6(B)</t>
+          <t>P5-TBAI1-6(B)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>C5S4-13/-6(B)</t>
+          <t>C5S4-13/P5-TBAI1-6(B)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>-6(B)/C5S4-13</t>
+          <t>P5-TBAI1-6(B)/C5S4-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -79608,17 +79608,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>-6(A)</t>
+          <t>P5-TBAI1-6(A)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C5S4-14/-6(A)</t>
+          <t>C5S4-14/P5-TBAI1-6(A)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>-6(A)/C5S4-14</t>
+          <t>P5-TBAI1-6(A)/C5S4-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -79658,17 +79658,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>-7(B)</t>
+          <t>P5-TBAI1-7(B)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>C5S4-15/-7(B)</t>
+          <t>C5S4-15/P5-TBAI1-7(B)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>-7(B)/C5S4-15</t>
+          <t>P5-TBAI1-7(B)/C5S4-15</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -79708,17 +79708,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>-7(A)</t>
+          <t>P5-TBAI1-7(A)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C5S4-16/-7(A)</t>
+          <t>C5S4-16/P5-TBAI1-7(A)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-7(A)/C5S4-16</t>
+          <t>P5-TBAI1-7(A)/C5S4-16</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -79758,17 +79758,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>-8(B)</t>
+          <t>P5-TBAI1-8(B)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>C5S4-17/-8(B)</t>
+          <t>C5S4-17/P5-TBAI1-8(B)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>-8(B)/C5S4-17</t>
+          <t>P5-TBAI1-8(B)/C5S4-17</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -79806,17 +79806,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>-8(A)</t>
+          <t>P5-TBAI1-8(A)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>C5S4-18/-8(A)</t>
+          <t>C5S4-18/P5-TBAI1-8(A)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>-8(A)/C5S4-18</t>
+          <t>P5-TBAI1-8(A)/C5S4-18</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -79854,17 +79854,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>-9(B)</t>
+          <t>P5-TBAI1-9(B)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>C5S4-19/-9(B)</t>
+          <t>C5S4-19/P5-TBAI1-9(B)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>-9(B)/C5S4-19</t>
+          <t>P5-TBAI1-9(B)/C5S4-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -79902,17 +79902,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>-9(A)</t>
+          <t>P5-TBAI1-9(A)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C5S4-20/-9(A)</t>
+          <t>C5S4-20/P5-TBAI1-9(A)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>-9(A)/C5S4-20</t>
+          <t>P5-TBAI1-9(A)/C5S4-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -79950,17 +79950,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>-10(B)</t>
+          <t>P5-TBAI1-10(B)</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>C5S4-21/-10(B)</t>
+          <t>C5S4-21/P5-TBAI1-10(B)</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>-10(B)/C5S4-21</t>
+          <t>P5-TBAI1-10(B)/C5S4-21</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -80000,17 +80000,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>-10(A)</t>
+          <t>P5-TBAI1-10(A)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>C5S4-22/-10(A)</t>
+          <t>C5S4-22/P5-TBAI1-10(A)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-10(A)/C5S4-22</t>
+          <t>P5-TBAI1-10(A)/C5S4-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -80050,17 +80050,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>-11(B)</t>
+          <t>P5-TBAI1-11(B)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>C5S4-23/-11(B)</t>
+          <t>C5S4-23/P5-TBAI1-11(B)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-11(B)/C5S4-23</t>
+          <t>P5-TBAI1-11(B)/C5S4-23</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -80100,17 +80100,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>-11(A)</t>
+          <t>P5-TBAI1-11(A)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>C5S4-24/-11(A)</t>
+          <t>C5S4-24/P5-TBAI1-11(A)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>-11(A)/C5S4-24</t>
+          <t>P5-TBAI1-11(A)/C5S4-24</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -80150,17 +80150,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>-12(B)</t>
+          <t>P5-TBAI1-12(B)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>C5S4-25/-12(B)</t>
+          <t>C5S4-25/P5-TBAI1-12(B)</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>-12(B)/C5S4-25</t>
+          <t>P5-TBAI1-12(B)/C5S4-25</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -80200,17 +80200,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-12(A)</t>
+          <t>P5-TBAI1-12(A)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>C5S4-26/-12(A)</t>
+          <t>C5S4-26/P5-TBAI1-12(A)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-12(A)/C5S4-26</t>
+          <t>P5-TBAI1-12(A)/C5S4-26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -80350,17 +80350,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>-13(B)</t>
+          <t>P5-TBAI1-13(B)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>C5S4-29/-13(B)</t>
+          <t>C5S4-29/P5-TBAI1-13(B)</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>-13(B)/C5S4-29</t>
+          <t>P5-TBAI1-13(B)/C5S4-29</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -80400,17 +80400,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>-13(A)</t>
+          <t>P5-TBAI1-13(A)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>C5S4-30/-13(A)</t>
+          <t>C5S4-30/P5-TBAI1-13(A)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-13(A)/C5S4-30</t>
+          <t>P5-TBAI1-13(A)/C5S4-30</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -80450,17 +80450,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>-14(B)</t>
+          <t>P5-TBAI1-14(B)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>C5S4-31/-14(B)</t>
+          <t>C5S4-31/P5-TBAI1-14(B)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>-14(B)/C5S4-31</t>
+          <t>P5-TBAI1-14(B)/C5S4-31</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -80500,17 +80500,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>-14(A)</t>
+          <t>P5-TBAI1-14(A)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>C5S4-32/-14(A)</t>
+          <t>C5S4-32/P5-TBAI1-14(A)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-14(A)/C5S4-32</t>
+          <t>P5-TBAI1-14(A)/C5S4-32</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -80550,17 +80550,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>-15(B)</t>
+          <t>P5-TBAI1-15(B)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>C5S4-33/-15(B)</t>
+          <t>C5S4-33/P5-TBAI1-15(B)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>-15(B)/C5S4-33</t>
+          <t>P5-TBAI1-15(B)/C5S4-33</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -80600,17 +80600,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>-15(A)</t>
+          <t>P5-TBAI1-15(A)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C5S4-34/-15(A)</t>
+          <t>C5S4-34/P5-TBAI1-15(A)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>-15(A)/C5S4-34</t>
+          <t>P5-TBAI1-15(A)/C5S4-34</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -80650,17 +80650,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>-16(B)</t>
+          <t>P5-TBAI1-16(B)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>C5S4-35/-16(B)</t>
+          <t>C5S4-35/P5-TBAI1-16(B)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>-16(B)/C5S4-35</t>
+          <t>P5-TBAI1-16(B)/C5S4-35</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -80700,17 +80700,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>-16(A)</t>
+          <t>P5-TBAI1-16(A)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>C5S4-36/-16(A)</t>
+          <t>C5S4-36/P5-TBAI1-16(A)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>-16(A)/C5S4-36</t>
+          <t>P5-TBAI1-16(A)/C5S4-36</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">

--- a/03_IO_Lists_and_Schedules/IO_List-By_SlotConfig.xlsx
+++ b/03_IO_Lists_and_Schedules/IO_List-By_SlotConfig.xlsx
@@ -3599,8 +3599,10 @@
           <t>XA-60202A</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -3647,8 +3649,10 @@
           <t>XA-60202B</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -3695,8 +3699,10 @@
           <t>XA-60202C</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -3743,8 +3749,10 @@
           <t>XA-60202D</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -3791,8 +3799,10 @@
           <t>XA-60202E</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -3839,8 +3849,10 @@
           <t>XA-60202F</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -3887,8 +3899,10 @@
           <t>XA-60202G</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -3935,8 +3949,10 @@
           <t>XA-60202H</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -3983,8 +3999,10 @@
           <t>XA-60202I</t>
         </is>
       </c>
-      <c r="I14" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -4031,8 +4049,10 @@
           <t>XA-60202J</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -4079,8 +4099,10 @@
           <t>XA-60202K</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -4127,8 +4149,10 @@
           <t>XA-60202L</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -4175,8 +4199,10 @@
           <t>XA-60202M</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -4223,8 +4249,10 @@
           <t>XV-60202</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -4271,8 +4299,10 @@
           <t>XV-60202</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -4319,8 +4349,10 @@
           <t>XV-60205A</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -4467,8 +4499,10 @@
           <t>XV-60205A</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -4515,8 +4549,10 @@
           <t>XV-60240D</t>
         </is>
       </c>
-      <c r="I25" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -4563,8 +4599,10 @@
           <t>XV-60240D</t>
         </is>
       </c>
-      <c r="I26" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -4611,8 +4649,10 @@
           <t>XV-60240D</t>
         </is>
       </c>
-      <c r="I27" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -4659,8 +4699,10 @@
           <t>XV-60240D</t>
         </is>
       </c>
-      <c r="I28" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -4707,8 +4749,10 @@
           <t>YA-60205</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -4755,8 +4799,10 @@
           <t>YI-60205</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -6375,8 +6421,10 @@
           <t>XV-40202E</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -6423,8 +6471,10 @@
           <t>XV-40202F</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -6471,8 +6521,10 @@
           <t>XV-40202G</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -6519,8 +6571,10 @@
           <t>XV-40202H</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -6567,8 +6621,10 @@
           <t>XV-40203B</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -6615,8 +6671,10 @@
           <t>XV-40203C</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -6663,8 +6721,10 @@
           <t>XV-40203D</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -6711,8 +6771,10 @@
           <t>XV-40203E</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -6759,8 +6821,10 @@
           <t>SV-40201</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -6807,8 +6871,10 @@
           <t>SV-40202</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -6855,8 +6921,10 @@
           <t>SV-40203</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -6903,8 +6971,10 @@
           <t>SV-40204</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -6951,8 +7021,10 @@
           <t>XV-40201A</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -6999,8 +7071,10 @@
           <t>XV-40201B</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -7047,8 +7121,10 @@
           <t>XV-40201C</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -7095,8 +7171,10 @@
           <t>XV-40201D</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -7365,8 +7443,10 @@
           <t>XV-40201E</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -7413,8 +7493,10 @@
           <t>XV-40201F</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -7461,8 +7543,10 @@
           <t>XV-40201G</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -7509,8 +7593,10 @@
           <t>XV-40201H</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -7557,8 +7643,10 @@
           <t>XV-40202A</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -7605,8 +7693,10 @@
           <t>XV-40202B</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -7653,8 +7743,10 @@
           <t>XV-40202C</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -7701,8 +7793,10 @@
           <t>XV-40202D</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -8249,8 +8343,10 @@
           <t>SV-60201</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -8297,8 +8393,10 @@
           <t>SV-60202</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -8345,8 +8443,10 @@
           <t>SV-60230</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -8393,8 +8493,10 @@
           <t>SV-60203</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -8441,8 +8543,10 @@
           <t>SV-60240A</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -8489,8 +8593,10 @@
           <t>SV-60231</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -8537,8 +8643,10 @@
           <t>SV-60240B</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -8585,8 +8693,10 @@
           <t>SV-60240C</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -8633,8 +8743,10 @@
           <t>XV-60240D</t>
         </is>
       </c>
-      <c r="I32" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -8681,8 +8793,10 @@
           <t>XV-60251</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -8729,8 +8843,10 @@
           <t>XV-60202</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -8777,8 +8893,10 @@
           <t>XV-60205A</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -11169,8 +11287,10 @@
           <t>DPI-60240</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -11217,8 +11337,10 @@
           <t>DPI-60240</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -11365,8 +11487,10 @@
           <t>FT-60201</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -11413,8 +11537,10 @@
           <t>FT-60201</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -11461,8 +11587,10 @@
           <t>FT-60204</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -11509,8 +11637,10 @@
           <t>FT-60204</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -11657,8 +11787,10 @@
           <t>FT-61307</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -11705,8 +11837,10 @@
           <t>FT-61307</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -14614,7 +14748,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
@@ -14664,7 +14798,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
@@ -14712,8 +14846,10 @@
           <t>XV-40203F</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -14760,8 +14896,10 @@
           <t>XV-40203F</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -14808,8 +14946,10 @@
           <t>XV-40204B</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -14856,8 +14996,10 @@
           <t>XV-40204B</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -14904,8 +15046,10 @@
           <t>XV-40204C</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -14952,8 +15096,10 @@
           <t>XV-40204C</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -15000,8 +15146,10 @@
           <t>XV-40205A</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -15048,8 +15196,10 @@
           <t>XV-40205A</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -15096,8 +15246,10 @@
           <t>XV-40205B</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -15144,8 +15296,10 @@
           <t>XV-40205B</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -15292,8 +15446,10 @@
           <t>XV-40205C</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -15340,8 +15496,10 @@
           <t>XV-40205C</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -15388,8 +15546,10 @@
           <t>XV-40205D</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -15436,8 +15596,10 @@
           <t>XV-40205D</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -15484,8 +15646,10 @@
           <t>XV-40205F</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -15532,8 +15696,10 @@
           <t>XV-40205F</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -15580,8 +15746,10 @@
           <t>XV-40222</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -15628,8 +15796,10 @@
           <t>XV-40222</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -16298,8 +16468,10 @@
           <t>FT-60202</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -16346,8 +16518,10 @@
           <t>LSH-60251</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -16394,8 +16568,10 @@
           <t>PSL-60220</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -16442,8 +16618,10 @@
           <t>TSH-60230</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -16490,8 +16668,10 @@
           <t>TSH-60240</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -16538,8 +16718,10 @@
           <t>TSH-60241A</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -16586,8 +16768,10 @@
           <t>TSH-60242A</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -16634,8 +16818,10 @@
           <t>TSH-60243A</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -16682,8 +16868,10 @@
           <t>TSL-60241B</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -16730,8 +16918,10 @@
           <t>TSL-60242B</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -16778,8 +16968,10 @@
           <t>TSL-60243B</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -16826,8 +17018,10 @@
           <t>XA-60240A</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -16874,8 +17068,10 @@
           <t>XA-60240B</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -16922,8 +17118,10 @@
           <t>XA-60241A</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -16970,8 +17168,10 @@
           <t>XA-60241B</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -17018,8 +17218,10 @@
           <t>XA-60242A</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -17166,8 +17368,10 @@
           <t>XA-60242B</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -17214,8 +17418,10 @@
           <t>XA-60243A</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -17262,8 +17468,10 @@
           <t>XA-60243B</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -17310,8 +17518,10 @@
           <t>XV-60214</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -17358,8 +17568,10 @@
           <t>XV-60214</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -17406,8 +17618,10 @@
           <t>XV-60241</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -17454,8 +17668,10 @@
           <t>XV-60241</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -19013,8 +19229,10 @@
           <t>XA-FH-60210A</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -19061,8 +19279,10 @@
           <t>XA-FH-60210B</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -19109,8 +19329,10 @@
           <t>XA-FH-60210C</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -19157,8 +19379,10 @@
           <t>XA-FH-60210D</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -19205,8 +19429,10 @@
           <t>XA-FH-60210E</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -19403,8 +19629,10 @@
           <t>SV-60207</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -19451,8 +19679,10 @@
           <t>SV-60207</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -19499,8 +19729,10 @@
           <t>XV-60264</t>
         </is>
       </c>
-      <c r="I16" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -19547,8 +19779,10 @@
           <t>XV-60264</t>
         </is>
       </c>
-      <c r="I17" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -19595,8 +19829,10 @@
           <t>XV-60264FN</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -19643,8 +19879,10 @@
           <t>XV-60264FN</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -19691,8 +19929,10 @@
           <t>XV-60264FP</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -19739,8 +19979,10 @@
           <t>XV-60264FP</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -19887,8 +20129,10 @@
           <t>XV-60201</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -19935,8 +20179,10 @@
           <t>XV-60201</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -19983,8 +20229,10 @@
           <t>XV-60264FQ</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -20031,8 +20279,10 @@
           <t>XV-60264FQ</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -20079,8 +20329,10 @@
           <t>XV-60261</t>
         </is>
       </c>
-      <c r="I28" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -20127,8 +20379,10 @@
           <t>XV-60261</t>
         </is>
       </c>
-      <c r="I29" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -20175,8 +20429,10 @@
           <t>XV-60264FR</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -20223,8 +20479,10 @@
           <t>XV-60264FR</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -20271,8 +20529,10 @@
           <t>XV-60261FA</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -20319,8 +20579,10 @@
           <t>XV-60261FA</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -20367,8 +20629,10 @@
           <t>XV-60264SN</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -20415,8 +20679,10 @@
           <t>XV-60264SN</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -20463,8 +20729,10 @@
           <t>XV-60261FB</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -20511,8 +20779,10 @@
           <t>XV-60261FB</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -20559,8 +20829,10 @@
           <t>XV-60264SP</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -20607,8 +20879,10 @@
           <t>XV-60264SP</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -20877,8 +21151,10 @@
           <t>XV-60261FC</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -20925,8 +21201,10 @@
           <t>XV-60261FC</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -20973,8 +21251,10 @@
           <t>XV-60264SQ</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -21021,8 +21301,10 @@
           <t>XV-60264SQ</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -21069,8 +21351,10 @@
           <t>XV-60261FD</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -21117,8 +21401,10 @@
           <t>XV-60261FD</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -21165,8 +21451,10 @@
           <t>XV-60264SR</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -21213,8 +21501,10 @@
           <t>XV-60264SR</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -21261,8 +21551,10 @@
           <t>XV-60261SA</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -21309,8 +21601,10 @@
           <t>XV-60261SA</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -21357,8 +21651,10 @@
           <t>XV-60261SB</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -21405,8 +21701,10 @@
           <t>XV-60261SB</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -21453,8 +21751,10 @@
           <t>XV-60261SC</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -21501,8 +21801,10 @@
           <t>XV-60261SC</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -21549,8 +21851,10 @@
           <t>XV-60261SD</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -21597,8 +21901,10 @@
           <t>XV-60261SD</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -21745,8 +22051,10 @@
           <t>XV-60262</t>
         </is>
       </c>
-      <c r="I24" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -21793,8 +22101,10 @@
           <t>XV-60262</t>
         </is>
       </c>
-      <c r="I25" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -21841,8 +22151,10 @@
           <t>XV-60262FE</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -21889,8 +22201,10 @@
           <t>XV-60262FE</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -21937,8 +22251,10 @@
           <t>XV-60262FF</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -21985,8 +22301,10 @@
           <t>XV-60262FF</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -22033,8 +22351,10 @@
           <t>XV-60262FG</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -22081,8 +22401,10 @@
           <t>XV-60262FG</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -22129,8 +22451,10 @@
           <t>XV-60262FH</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -22177,8 +22501,10 @@
           <t>XV-60262FH</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -22225,8 +22551,10 @@
           <t>XV-60262SE</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -22273,8 +22601,10 @@
           <t>XV-60262SE</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -22321,8 +22651,10 @@
           <t>XV-60262SF</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -22369,8 +22701,10 @@
           <t>XV-60262SF</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -22417,8 +22751,10 @@
           <t>XV-60262SG</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -22465,8 +22801,10 @@
           <t>XV-60262SG</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -22735,8 +23073,10 @@
           <t>XV-60262SH</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -22783,8 +23123,10 @@
           <t>XV-60262SH</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -22831,8 +23173,10 @@
           <t>XV-60263</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -22879,8 +23223,10 @@
           <t>XV-60263</t>
         </is>
       </c>
-      <c r="I9" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -22927,8 +23273,10 @@
           <t>XV-60263FJ</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -22975,8 +23323,10 @@
           <t>XV-60263FJ</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -23023,8 +23373,10 @@
           <t>XV-60263FK</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -23071,8 +23423,10 @@
           <t>XV-60263FK</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -23119,8 +23473,10 @@
           <t>XV-60263FL</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -23167,8 +23523,10 @@
           <t>XV-60263FL</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -23215,8 +23573,10 @@
           <t>XV-60263FM</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -23263,8 +23623,10 @@
           <t>XV-60263FM</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -23311,8 +23673,10 @@
           <t>XV-60263SJ</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -23359,8 +23723,10 @@
           <t>XV-60263SJ</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -23407,8 +23773,10 @@
           <t>XV-60263SK</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -23455,8 +23823,10 @@
           <t>XV-60263SK</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -23603,8 +23973,10 @@
           <t>XV-60263SL</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -23651,8 +24023,10 @@
           <t>XV-60263SL</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -23699,8 +24073,10 @@
           <t>XV-60263SM</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -23747,8 +24123,10 @@
           <t>XV-60263SM</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -24617,8 +24995,10 @@
           <t>XV-40203F</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -24665,8 +25045,10 @@
           <t>XV-40204B</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -24713,8 +25095,10 @@
           <t>XV-40204C</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -24761,8 +25145,10 @@
           <t>XV-40205A</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -24809,8 +25195,10 @@
           <t>XV-40205B</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -24857,8 +25245,10 @@
           <t>XV-40205C</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -24905,8 +25295,10 @@
           <t>XV-40205D</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -24953,8 +25345,10 @@
           <t>XV-40205F</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -25001,8 +25395,10 @@
           <t>XV-40222</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -25499,8 +25895,10 @@
           <t>XS-60240B</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -25547,8 +25945,10 @@
           <t>XV-60214</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -25595,8 +25995,10 @@
           <t>XV-60241</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -26515,8 +26917,10 @@
           <t>SV-60207</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -26563,8 +26967,10 @@
           <t>XS-FH-60210C</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -26611,8 +27017,10 @@
           <t>XS-FH-60210D</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -26659,8 +27067,10 @@
           <t>XV-60201</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -26707,8 +27117,10 @@
           <t>XV-60261</t>
         </is>
       </c>
-      <c r="I10" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -26755,8 +27167,10 @@
           <t>XV-60261FA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -26803,8 +27217,10 @@
           <t>XV-60261FB</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -26851,8 +27267,10 @@
           <t>XV-60261FC</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -26899,8 +27317,10 @@
           <t>XV-60261FD</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -26947,8 +27367,10 @@
           <t>XV-60261SA</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -26995,8 +27417,10 @@
           <t>XV-60261SB</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -27043,8 +27467,10 @@
           <t>XV-60261SC</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -27091,8 +27517,10 @@
           <t>XV-60261SD</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -27139,8 +27567,10 @@
           <t>XV-60262</t>
         </is>
       </c>
-      <c r="I19" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -27187,8 +27617,10 @@
           <t>XV-60262FE</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -27235,8 +27667,10 @@
           <t>XV-60262FF</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -27383,8 +27817,10 @@
           <t>XV-60262FG</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -27431,8 +27867,10 @@
           <t>XV-60262FH</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -27479,8 +27917,10 @@
           <t>XV-60262SE</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -27527,8 +27967,10 @@
           <t>XV-60262SF</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -27575,8 +28017,10 @@
           <t>XV-60262SG</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -27623,8 +28067,10 @@
           <t>XV-60262SH</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -27671,8 +28117,10 @@
           <t>XV-60263</t>
         </is>
       </c>
-      <c r="I30" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -27719,8 +28167,10 @@
           <t>XV-60263FJ</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -27767,8 +28217,10 @@
           <t>XV-60263FK</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -27815,8 +28267,10 @@
           <t>XV-60263FL</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -27863,8 +28317,10 @@
           <t>XV-60263FM</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -27911,8 +28367,10 @@
           <t>XV-60263SJ</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -27959,8 +28417,10 @@
           <t>XV-60263SK</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -28007,8 +28467,10 @@
           <t>XV-60263SL</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -28055,8 +28517,10 @@
           <t>XV-60263SM</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -28375,8 +28839,10 @@
           <t>XV-60264</t>
         </is>
       </c>
-      <c r="I6" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -28423,8 +28889,10 @@
           <t>XV-60264FN</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -28471,8 +28939,10 @@
           <t>XV-60264FP</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -28519,8 +28989,10 @@
           <t>XV-60264FQ</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -28567,8 +29039,10 @@
           <t>XV-60264FR</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -28615,8 +29089,10 @@
           <t>XV-60264SN</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -28663,8 +29139,10 @@
           <t>XV-60264SP</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -28711,8 +29189,10 @@
           <t>XV-60264SQ</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -28759,8 +29239,10 @@
           <t>XV-60264SR</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -30879,8 +31361,10 @@
           <t>TT-40221</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -30927,8 +31411,10 @@
           <t>TT-40221</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -30975,8 +31461,10 @@
           <t>TT-40222</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -31023,8 +31511,10 @@
           <t>TT-40222</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -32393,8 +32883,10 @@
           <t>FT-60202</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -32441,8 +32933,10 @@
           <t>FT-60202</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -33089,8 +33583,10 @@
           <t>TT-60210</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -33137,8 +33633,10 @@
           <t>TT-60210</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -33185,8 +33683,10 @@
           <t>TT-60210A</t>
         </is>
       </c>
-      <c r="I26" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -33233,8 +33733,10 @@
           <t>TT-60210A</t>
         </is>
       </c>
-      <c r="I27" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -33281,8 +33783,10 @@
           <t>TT-60210B</t>
         </is>
       </c>
-      <c r="I28" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -33329,8 +33833,10 @@
           <t>TT-60210B</t>
         </is>
       </c>
-      <c r="I29" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -33377,8 +33883,10 @@
           <t>TT-60211</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -33425,8 +33933,10 @@
           <t>TT-60211</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -33573,8 +34083,10 @@
           <t>TT-60212A</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -33621,8 +34133,10 @@
           <t>TT-60212A</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -33669,8 +34183,10 @@
           <t>TT-60212B</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -33717,8 +34233,10 @@
           <t>TT-60212B</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -33765,8 +34283,10 @@
           <t>TT-60214</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -33813,8 +34333,10 @@
           <t>TT-60214</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -33861,8 +34383,10 @@
           <t>TT-60215A</t>
         </is>
       </c>
-      <c r="I40" s="10" t="n">
-        <v>0</v>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
@@ -33909,8 +34433,10 @@
           <t>TT-60215A</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
@@ -40374,8 +40900,10 @@
           <t>FT-60203</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -40422,8 +40950,10 @@
           <t>LSH-60250</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -40470,8 +41000,10 @@
           <t>XA-60261</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -40518,8 +41050,10 @@
           <t>XA-60262</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -41388,8 +41922,10 @@
           <t>PSL-61305</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -41436,8 +41972,10 @@
           <t>PSL-61306</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -41484,8 +42022,10 @@
           <t>PVM-61301</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -41532,8 +42072,10 @@
           <t>PVM-61301</t>
         </is>
       </c>
-      <c r="I9" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -41580,8 +42122,10 @@
           <t>XA-61301A</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -41628,8 +42172,10 @@
           <t>XA-61301B</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -41676,8 +42222,10 @@
           <t>XA-61301C</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -41724,8 +42272,10 @@
           <t>XA-61301D</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -41772,8 +42322,10 @@
           <t>XA-61301E</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -41820,8 +42372,10 @@
           <t>XA-61301F</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -41868,8 +42422,10 @@
           <t>XA-61301G</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -41916,8 +42472,10 @@
           <t>XA-61301H</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -41964,8 +42522,10 @@
           <t>XA-61301J</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -42012,8 +42572,10 @@
           <t>XV-61302</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -42060,8 +42622,10 @@
           <t>XV-61302</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -42108,8 +42672,10 @@
           <t>XV-61303</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -42256,8 +42822,10 @@
           <t>XV-61303</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -43276,8 +43844,10 @@
           <t>DV-61301</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -43324,8 +43894,10 @@
           <t>DV-61301</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -43372,8 +43944,10 @@
           <t>DV-61302</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -43420,8 +43994,10 @@
           <t>DV-61302</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -43468,8 +44044,10 @@
           <t>LS-61303</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -43516,8 +44094,10 @@
           <t>PSL-61301</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -43564,8 +44144,10 @@
           <t>PSL-61302</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -43612,8 +44194,10 @@
           <t>PSL-61311</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -43660,8 +44244,10 @@
           <t>SV-61304</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -43708,8 +44294,10 @@
           <t>SV-61304</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -43756,8 +44344,10 @@
           <t>XV-61301</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -43804,8 +44394,10 @@
           <t>XV-61301</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -45574,8 +46166,10 @@
           <t>SV-60220</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -46072,8 +46666,10 @@
           <t>PVM-61301</t>
         </is>
       </c>
-      <c r="I24" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -46120,8 +46716,10 @@
           <t>PVM-61301</t>
         </is>
       </c>
-      <c r="I25" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -46168,8 +46766,10 @@
           <t>SV-61307</t>
         </is>
       </c>
-      <c r="I26" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -46216,8 +46816,10 @@
           <t>SV-61308</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -46264,8 +46866,10 @@
           <t>SV-61309</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -46312,8 +46916,10 @@
           <t>SV-61310</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -46360,8 +46966,10 @@
           <t>SV-61311</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -46408,8 +47016,10 @@
           <t>XS-61301A</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -46456,8 +47066,10 @@
           <t>XS-61301B</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -46504,8 +47116,10 @@
           <t>XS-61301C</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -46552,8 +47166,10 @@
           <t>XS-61301D</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -46600,8 +47216,10 @@
           <t>XS-61301E</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -46648,8 +47266,10 @@
           <t>XS-61301F</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -46696,8 +47316,10 @@
           <t>XV-61302</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -46744,8 +47366,10 @@
           <t>XV-61303</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -47064,8 +47688,10 @@
           <t>DV-61301</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -47112,8 +47738,10 @@
           <t>DV-61302</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -47160,8 +47788,10 @@
           <t>SV-61301</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -47208,8 +47838,10 @@
           <t>SV-61302</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -47256,8 +47888,10 @@
           <t>SV-61303</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -47304,8 +47938,10 @@
           <t>SV-61304</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -47352,8 +47988,10 @@
           <t>SV-61305</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -47400,8 +48038,10 @@
           <t>SV-61306</t>
         </is>
       </c>
-      <c r="I13" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -47448,8 +48088,10 @@
           <t>XV-61301</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -48968,8 +49610,10 @@
           <t>TT-60215B</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -49016,8 +49660,10 @@
           <t>TT-60215B</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -49064,8 +49710,10 @@
           <t>TT-60216</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -49112,8 +49760,10 @@
           <t>TT-60216</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -49160,8 +49810,10 @@
           <t>TT-60240</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -49208,8 +49860,10 @@
           <t>TT-60240</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -49256,8 +49910,10 @@
           <t>TT-60241A</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -49304,8 +49960,10 @@
           <t>TT-60241A</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -49452,8 +50110,10 @@
           <t>TT-60241B</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -49500,8 +50160,10 @@
           <t>TT-60241B</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -49548,8 +50210,10 @@
           <t>VT-60210A</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -49596,8 +50260,10 @@
           <t>VT-60210A</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -49644,8 +50310,10 @@
           <t>VT-60210B</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -49692,8 +50360,10 @@
           <t>VT-60210B</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -49740,8 +50410,10 @@
           <t>VT-60241A</t>
         </is>
       </c>
-      <c r="I22" s="10" t="n">
-        <v>0</v>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -49788,8 +50460,10 @@
           <t>VT-60241A</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
@@ -49836,8 +50510,10 @@
           <t>VT-60241B</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -49884,8 +50560,10 @@
           <t>VT-60241B</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Vibration Transmitter</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -49932,8 +50610,10 @@
           <t>FT-60210</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -49980,8 +50660,10 @@
           <t>FT-60210</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -50028,8 +50710,10 @@
           <t>FT-60211</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -50076,8 +50760,10 @@
           <t>FT-60211</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -50124,8 +50810,10 @@
           <t>FT-60210</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -50172,8 +50860,10 @@
           <t>FT-60210</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -50320,8 +51010,10 @@
           <t>FT-60211</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -50368,8 +51060,10 @@
           <t>FT-60211</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -50616,8 +51310,10 @@
           <t>FT-60203</t>
         </is>
       </c>
-      <c r="I40" s="10" t="n">
-        <v>0</v>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
@@ -50664,8 +51360,10 @@
           <t>FT-60203</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
@@ -50834,8 +51532,10 @@
           <t>FT-60207</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -50882,8 +51582,10 @@
           <t>FT-60207</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -50930,8 +51632,10 @@
           <t>FT-60221</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -50978,8 +51682,10 @@
           <t>FT-60221</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -51026,8 +51732,10 @@
           <t>FT-60261FA</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -51074,8 +51782,10 @@
           <t>FT-60261FA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -51122,8 +51832,10 @@
           <t>FT-60261FB</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -51170,8 +51882,10 @@
           <t>FT-60261FB</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -51318,8 +52032,10 @@
           <t>FT-60261FC</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -51366,8 +52082,10 @@
           <t>FT-60261FC</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -51414,8 +52132,10 @@
           <t>FT-60261FD</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -51462,8 +52182,10 @@
           <t>FT-60261FD</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -51510,8 +52232,10 @@
           <t>FT-60262FE</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -51558,8 +52282,10 @@
           <t>FT-60262FE</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -51606,8 +52332,10 @@
           <t>FT-60262FF</t>
         </is>
       </c>
-      <c r="I22" s="10" t="n">
-        <v>0</v>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -51654,8 +52382,10 @@
           <t>FT-60262FF</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
@@ -51702,8 +52432,10 @@
           <t>FT-60262FG</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -51750,8 +52482,10 @@
           <t>FT-60262FG</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -51798,8 +52532,10 @@
           <t>FT-60262FH</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -51846,8 +52582,10 @@
           <t>FT-60262FH</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -51894,8 +52632,10 @@
           <t>FT-60263FJ</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -51942,8 +52682,10 @@
           <t>FT-60263FJ</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -51990,8 +52732,10 @@
           <t>FT-60263FK</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -52038,8 +52782,10 @@
           <t>FT-60263FK</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -52186,8 +52932,10 @@
           <t>FT-60263FL</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -52234,8 +52982,10 @@
           <t>FT-60263FL</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -52282,8 +53032,10 @@
           <t>FT-60263FM</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -52330,8 +53082,10 @@
           <t>FT-60263FM</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -52378,8 +53132,10 @@
           <t>FT-60264FN</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -52426,8 +53182,10 @@
           <t>FT-60264FN</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -52474,8 +53232,10 @@
           <t>FT-60264FP</t>
         </is>
       </c>
-      <c r="I40" s="10" t="n">
-        <v>0</v>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
@@ -52522,8 +53282,10 @@
           <t>FT-60264FP</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
@@ -52692,8 +53454,10 @@
           <t>FT-60264FQ</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -52740,8 +53504,10 @@
           <t>FT-60264FQ</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -52788,8 +53554,10 @@
           <t>FT-60264FR</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -52836,8 +53604,10 @@
           <t>FT-60264FR</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -53384,8 +54154,10 @@
           <t>TI-FH-60210</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Indicator / Sensor</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -53432,8 +54204,10 @@
           <t>TI-FH-60210</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Indicator / Sensor</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -53480,8 +54254,10 @@
           <t>TT-60201</t>
         </is>
       </c>
-      <c r="I22" s="10" t="n">
-        <v>0</v>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -53528,8 +54304,10 @@
           <t>TT-60201</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
@@ -53576,8 +54354,10 @@
           <t>TT-60202</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -53624,8 +54404,10 @@
           <t>TT-60202</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -53672,8 +54454,10 @@
           <t>TT-60207</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -53720,8 +54504,10 @@
           <t>TT-60207</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -53768,8 +54554,10 @@
           <t>UY-FH-60210A</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>I/P Converter Control Valve</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -53816,8 +54604,10 @@
           <t>UY-FH-60210A</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>I/P Converter Control Valve</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -54364,8 +55154,10 @@
           <t>TT-60245</t>
         </is>
       </c>
-      <c r="I40" s="10" t="n">
-        <v>0</v>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
@@ -54412,8 +55204,10 @@
           <t>TT-60245</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
@@ -55012,8 +55806,10 @@
           <t>PT-61306</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Pressure Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -55060,8 +55856,10 @@
           <t>PT-61306</t>
         </is>
       </c>
-      <c r="I9" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Pressure Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -55108,8 +55906,10 @@
           <t>TT-61303</t>
         </is>
       </c>
-      <c r="I10" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -55156,8 +55956,10 @@
           <t>TT-61303</t>
         </is>
       </c>
-      <c r="I11" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -55204,8 +56006,10 @@
           <t>TT-61304</t>
         </is>
       </c>
-      <c r="I12" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -55252,8 +56056,10 @@
           <t>TT-61304</t>
         </is>
       </c>
-      <c r="I13" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -57037,8 +57843,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -57242,17 +58048,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>P3-TBAO1-3</t>
+          <t>P3-TBAO1-1</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>C3S12-3/P3-TBAO1-3</t>
+          <t>C3S12-3/P3-TBAO1-1</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>P3-TBAO1-3/C3S12-3</t>
+          <t>P3-TBAO1-1/C3S12-3</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -57262,22 +58068,22 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Spare_AO_3</t>
+          <t>TCV-40222_AO_1</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>TCV-40222</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Spare Reserve Channel</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
-        <is>
-          <t>SPARE</t>
+          <t>Temperature Control Valve</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -57292,42 +58098,42 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>P3-TBAO1-4</t>
+          <t>P3-TBAO1-5</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>C3S12-4/P3-TBAO1-4</t>
+          <t>C3S12-4/P3-TBAO1-5</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>P3-TBAO1-4/C3S12-4</t>
+          <t>P3-TBAO1-5/C3S12-4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-607</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Spare_AO_4</t>
+          <t>UY-FH-60210B_AO_1</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>UY-FH-60210B</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Spare Reserve Channel</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
-        <is>
-          <t>SPARE</t>
+          <t>I/P Converter Control Valve</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -57542,42 +58348,42 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>P3-TBAO1-9</t>
+          <t>P3-TBAO1-2</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>C3S12-9/P3-TBAO1-9</t>
+          <t>C3S12-9/P3-TBAO1-2</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>P3-TBAO1-9/C3S12-9</t>
+          <t>P3-TBAO1-2/C3S12-9</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-602</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Spare_AO_9</t>
+          <t>TV-60202_AO_1</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>TV-60202</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Spare Reserve Channel</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
-        <is>
-          <t>SPARE</t>
+          <t>Temperature Control Valve</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -57592,27 +58398,27 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>P3-TBAO1-10</t>
+          <t>P3-TBAO1-6</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>C3S12-10/P3-TBAO1-10</t>
+          <t>C3S12-10/P3-TBAO1-6</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>P3-TBAO1-10/C3S12-10</t>
+          <t>P3-TBAO1-6/C3S12-10</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-607</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Spare_AO_10</t>
+          <t>Spare_AO_0</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -57742,42 +58548,42 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>P3-TBAO1-13</t>
+          <t>P3-TBAO1-3</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>C3S12-13/P3-TBAO1-13</t>
+          <t>C3S12-13/P3-TBAO1-3</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>P3-TBAO1-13/C3S12-13</t>
+          <t>P3-TBAO1-3/C3S12-13</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-602</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Spare_AO_13</t>
+          <t>TV-60214_AO_1</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>TV-60214</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Spare Reserve Channel</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
-        <is>
-          <t>SPARE</t>
+          <t>Temperature Control Valve</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -57792,27 +58598,27 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>P3-TBAO1-14</t>
+          <t>P3-TBAO1-7</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C3S12-14/P3-TBAO1-14</t>
+          <t>C3S12-14/P3-TBAO1-7</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>P3-TBAO1-14/C3S12-14</t>
+          <t>P3-TBAO1-7/C3S12-14</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-607</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Spare_AO_14</t>
+          <t>Spare_AO_0</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -58042,42 +58848,42 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>P3-TBAO1-19</t>
+          <t>P3-TBAO1-4</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>C3S12-19/P3-TBAO1-19</t>
+          <t>C3S12-19/P3-TBAO1-4</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>P3-TBAO1-19/C3S12-19</t>
+          <t>P3-TBAO1-4/C3S12-19</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-607</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Spare_AO_19</t>
+          <t>PV-60201_AO_1</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>PV-60201</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Spare Reserve Channel</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>SPARE</t>
+          <t>Pressure Control Valve</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -58092,27 +58898,27 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P3-TBAO1-20</t>
+          <t>P3-TBAO1-8</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C3S12-20/P3-TBAO1-20</t>
+          <t>C3S12-20/P3-TBAO1-8</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>P3-TBAO1-20/C3S12-20</t>
+          <t>P3-TBAO1-8/C3S12-20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>JB-402</t>
+          <t>JB-607</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Spare_AO_20</t>
+          <t>Spare_AO_0</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -59483,8 +60289,10 @@
           <t>AT-40201</t>
         </is>
       </c>
-      <c r="I6" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -59531,8 +60339,10 @@
           <t>AT-40202</t>
         </is>
       </c>
-      <c r="I7" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -59579,8 +60389,10 @@
           <t>AT-40203</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -59627,8 +60439,10 @@
           <t>LSH-60230</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -59675,8 +60489,10 @@
           <t>LSH-60231</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -59723,8 +60539,10 @@
           <t>LSH-60240</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -59771,8 +60589,10 @@
           <t>PD-60202</t>
         </is>
       </c>
-      <c r="I12" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -59819,8 +60639,10 @@
           <t>RV-60204</t>
         </is>
       </c>
-      <c r="I13" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -59867,8 +60689,10 @@
           <t>ZS-60201C</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -59915,8 +60739,10 @@
           <t>ZS-60201D</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -59963,8 +60789,10 @@
           <t>ZS-60201E</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -60011,8 +60839,10 @@
           <t>ZS-60229</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -60059,8 +60889,10 @@
           <t>ZS-60230</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -60107,8 +60939,10 @@
           <t>ZS-60231A</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -60155,8 +60989,10 @@
           <t>ZS-60231B</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -60353,8 +61189,10 @@
           <t>ZS-60201A</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -60401,8 +61239,10 @@
           <t>ZS-60201B</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -60449,8 +61289,10 @@
           <t>ZS-60231C</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -60497,8 +61339,10 @@
           <t>ZS-60231D</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -60545,8 +61389,10 @@
           <t>ZS-60231E</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -60593,8 +61439,10 @@
           <t>ZS-60231F</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -60641,8 +61489,10 @@
           <t>ZS-60240</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -61361,8 +62211,10 @@
           <t>ISV-61303</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -61409,8 +62261,10 @@
           <t>ISV-61304</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -61457,8 +62311,10 @@
           <t>LSH-61304</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -61505,8 +62361,10 @@
           <t>LSH-61305</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -61553,8 +62411,10 @@
           <t>LSH-61307</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -61601,8 +62461,10 @@
           <t>LSH-61312</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -61649,8 +62511,10 @@
           <t>PSE-61302</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -61697,8 +62561,10 @@
           <t>PSE-61303</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -61745,8 +62611,10 @@
           <t>RV-61301</t>
         </is>
       </c>
-      <c r="I14" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -61793,8 +62661,10 @@
           <t>RV-61304</t>
         </is>
       </c>
-      <c r="I15" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -61841,8 +62711,10 @@
           <t>RV-61305</t>
         </is>
       </c>
-      <c r="I16" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -61889,8 +62761,10 @@
           <t>SC-61301</t>
         </is>
       </c>
-      <c r="I17" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -61937,8 +62811,10 @@
           <t>SC-61302</t>
         </is>
       </c>
-      <c r="I18" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -61985,8 +62861,10 @@
           <t>ZS-61312</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -62033,8 +62911,10 @@
           <t>ZS-61313</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -63253,8 +64133,10 @@
           <t>ISV-61301</t>
         </is>
       </c>
-      <c r="I6" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -63301,8 +64183,10 @@
           <t>LSH-61301</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -63349,8 +64233,10 @@
           <t>LSH-61303</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -63397,8 +64283,10 @@
           <t>LSH-61306</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -63445,8 +64333,10 @@
           <t>LSH-61308</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -63493,8 +64383,10 @@
           <t>LSL-61302</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -63541,8 +64433,10 @@
           <t>PSE-61300</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -63589,8 +64483,10 @@
           <t>PSE-61301</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -63637,8 +64533,10 @@
           <t>PSE-61304</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -63685,8 +64583,10 @@
           <t>PSV-61301A</t>
         </is>
       </c>
-      <c r="I15" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -63733,8 +64633,10 @@
           <t>PSV-61301B</t>
         </is>
       </c>
-      <c r="I16" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -63781,8 +64683,10 @@
           <t>ZS-61310</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -63829,8 +64733,10 @@
           <t>ZS-61311</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -65549,8 +66455,10 @@
           <t>XA-60201</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -67599,8 +68507,10 @@
           <t>TT-60224</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -67647,8 +68557,10 @@
           <t>TT-60224</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -67695,8 +68607,10 @@
           <t>TT-60225</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -67743,8 +68657,10 @@
           <t>TT-60225</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -67891,8 +68807,10 @@
           <t>TT-60226</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -67939,8 +68857,10 @@
           <t>TT-60226</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -67987,8 +68907,10 @@
           <t>TT-60227</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -68035,8 +68957,10 @@
           <t>TT-60227</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -68083,8 +69007,10 @@
           <t>TT-60230</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -68131,8 +69057,10 @@
           <t>TT-60230</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -68379,8 +69307,10 @@
           <t>TT-60220</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -68427,8 +69357,10 @@
           <t>TT-60220</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -68475,8 +69407,10 @@
           <t>TT-60221</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -68523,8 +69457,10 @@
           <t>TT-60221</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -68571,8 +69507,10 @@
           <t>TT-60222</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -68619,8 +69557,10 @@
           <t>TT-60222</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -68767,8 +69707,10 @@
           <t>TT-60223</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -68815,8 +69757,10 @@
           <t>TT-60223</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -68863,8 +69807,10 @@
           <t>XT-60201</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Speed / Position Transmitter</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -68911,8 +69857,10 @@
           <t>XT-60201</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Speed / Position Transmitter</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -69381,8 +70329,10 @@
           <t>DPT-61312</t>
         </is>
       </c>
-      <c r="I8" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Differential Pressure Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -69429,8 +70379,10 @@
           <t>DPT-61312</t>
         </is>
       </c>
-      <c r="I9" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Differential Pressure Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -70477,8 +71429,10 @@
           <t>TT-61301</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -70525,8 +71479,10 @@
           <t>TT-61301</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -70673,8 +71629,10 @@
           <t>TT-61302</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -70721,8 +71679,10 @@
           <t>TT-61302</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -73322,8 +74282,10 @@
           <t>FS-20201</t>
         </is>
       </c>
-      <c r="I6" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -73370,8 +74332,10 @@
           <t>FT-913201</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -73418,8 +74382,10 @@
           <t>FT-936201</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -73466,8 +74432,10 @@
           <t>FT-936202</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -73514,8 +74482,10 @@
           <t>LSL-814201</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -73562,8 +74532,10 @@
           <t>PK-913201</t>
         </is>
       </c>
-      <c r="I11" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -73610,8 +74582,10 @@
           <t>PK-913202</t>
         </is>
       </c>
-      <c r="I12" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -73660,7 +74634,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
@@ -73710,7 +74684,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
@@ -73760,7 +74734,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
@@ -73810,7 +74784,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
@@ -73860,7 +74834,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
@@ -73910,7 +74884,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
@@ -73960,7 +74934,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
@@ -74008,8 +74982,10 @@
           <t>XA-80305A</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -74056,8 +75032,10 @@
           <t>XA-80305B</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -74204,8 +75182,10 @@
           <t>XA-80305C</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -74252,8 +75232,10 @@
           <t>XA-80305D</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -74300,8 +75282,10 @@
           <t>XA-80305E</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -74348,8 +75332,10 @@
           <t>XA-80305F</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -74396,8 +75382,10 @@
           <t>XA-80306A</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -74444,8 +75432,10 @@
           <t>XA-80306B</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -74492,8 +75482,10 @@
           <t>XA-80306C</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -74540,8 +75532,10 @@
           <t>XA-80306D</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -74588,8 +75582,10 @@
           <t>XA-80306E</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -74636,8 +75632,10 @@
           <t>XA-80306F</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -74684,8 +75682,10 @@
           <t>XV-20201</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -74732,8 +75732,10 @@
           <t>XV-20201</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -74780,8 +75782,10 @@
           <t>XV-20202</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -74828,8 +75832,10 @@
           <t>XV-20202</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -74876,8 +75882,10 @@
           <t>XV-20203</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -74924,8 +75932,10 @@
           <t>XV-20203</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -75194,8 +76204,10 @@
           <t>XV-20211</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -75242,8 +76254,10 @@
           <t>XV-20211</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -75290,8 +76304,10 @@
           <t>XV-20212</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -75338,8 +76354,10 @@
           <t>XV-20212</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -75386,8 +76404,10 @@
           <t>XV-20213</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -75434,8 +76454,10 @@
           <t>XV-20213</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -75482,8 +76504,10 @@
           <t>XV-913201</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -75530,8 +76554,10 @@
           <t>XV-913201</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -77100,8 +78126,10 @@
           <t>XA-92201</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -77148,8 +78176,10 @@
           <t>XV-20201</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -77196,8 +78226,10 @@
           <t>XV-20202</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -77244,8 +78276,10 @@
           <t>XV-20203</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -77292,8 +78326,10 @@
           <t>XV-20211</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -77340,8 +78376,10 @@
           <t>XV-20212</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -77388,8 +78426,10 @@
           <t>XV-20213</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -77436,8 +78476,10 @@
           <t>XV-913201</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -79006,8 +80048,10 @@
           <t>EXT-BIILER</t>
         </is>
       </c>
-      <c r="I6" s="10" t="e">
-        <v>#N/A</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>External Boiler 4-20mA Interface</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -79054,8 +80098,10 @@
           <t>EXT-BIILER</t>
         </is>
       </c>
-      <c r="I7" s="7" t="e">
-        <v>#N/A</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>External Boiler 4-20mA Interface</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -79102,8 +80148,10 @@
           <t>FT-913201</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -79150,8 +80198,10 @@
           <t>FT-913201</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -79198,8 +80248,10 @@
           <t>FT-913201</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -79246,8 +80298,10 @@
           <t>FT-913201</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -79294,8 +80348,10 @@
           <t>FT-936201</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -79342,8 +80398,10 @@
           <t>FT-936201</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -79490,8 +80548,10 @@
           <t>FT-936202</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -79538,8 +80598,10 @@
           <t>FT-936202</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Flow Transmitter</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -79786,8 +80848,10 @@
           <t>XT-92201</t>
         </is>
       </c>
-      <c r="I22" s="10" t="n">
-        <v>0</v>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Speed / Position Transmitter</t>
+        </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -79834,8 +80898,10 @@
           <t>XT-92201</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Speed / Position Transmitter</t>
+        </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
@@ -79882,8 +80948,10 @@
           <t>XV-913201</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -79930,8 +80998,10 @@
           <t>XV-913201</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -82002,7 +83072,7 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
@@ -82052,7 +83122,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
@@ -82102,7 +83172,7 @@
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
@@ -82152,7 +83222,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
@@ -82202,7 +83272,7 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
@@ -82252,7 +83322,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Valve With Position Switch </t>
+          <t>Manual Valve With Position Switch</t>
         </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
@@ -82300,8 +83370,10 @@
           <t>XV-40201A</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -82348,8 +83420,10 @@
           <t>XV-40201A</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -82396,8 +83470,10 @@
           <t>XV-40201B</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -82444,8 +83520,10 @@
           <t>XV-40201B</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -82492,8 +83570,10 @@
           <t>XV-40201C</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -82540,8 +83620,10 @@
           <t>XV-40201C</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -82810,8 +83892,10 @@
           <t>XV-40201D</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -82858,8 +83942,10 @@
           <t>XV-40201D</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -82906,8 +83992,10 @@
           <t>XV-40201E</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -82954,8 +84042,10 @@
           <t>XV-40201E</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
@@ -83002,8 +84092,10 @@
           <t>XV-40201F</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -83050,8 +84142,10 @@
           <t>XV-40201F</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
@@ -83098,8 +84192,10 @@
           <t>XV-40201G</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -83146,8 +84242,10 @@
           <t>XV-40201G</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
@@ -83194,8 +84292,10 @@
           <t>XV-40201H</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>0</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -83242,8 +84342,10 @@
           <t>XV-40201H</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
@@ -83290,8 +84392,10 @@
           <t>XV-40202A</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>0</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -83338,8 +84442,10 @@
           <t>XV-40202B</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
@@ -83386,8 +84492,10 @@
           <t>XV-40202B</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -83434,8 +84542,10 @@
           <t>XV-40202C</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
@@ -83482,8 +84592,10 @@
           <t>XV-40202C</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -83530,8 +84642,10 @@
           <t>XV-40202D</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
@@ -83678,8 +84792,10 @@
           <t>XV-40202D</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -83726,8 +84842,10 @@
           <t>XV-40202E</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
@@ -83774,8 +84892,10 @@
           <t>XV-40202A</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -83822,8 +84942,10 @@
           <t>XV-40202E</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -83870,8 +84992,10 @@
           <t>XV-40202F</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -83918,8 +85042,10 @@
           <t>XV-40202F</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -83966,8 +85092,10 @@
           <t>XV-40202G</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -84014,8 +85142,10 @@
           <t>XV-40202G</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -84062,8 +85192,10 @@
           <t>XV-40202H</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -84110,8 +85242,10 @@
           <t>XV-40202H</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
@@ -84158,8 +85292,10 @@
           <t>XV-40203B</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>0</v>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -84206,8 +85342,10 @@
           <t>XV-40203B</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
@@ -84254,8 +85392,10 @@
           <t>XV-40203C</t>
         </is>
       </c>
-      <c r="I36" s="10" t="n">
-        <v>0</v>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -84302,8 +85442,10 @@
           <t>XV-40203C</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
@@ -84350,8 +85492,10 @@
           <t>XV-40203D</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>0</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -84398,8 +85542,10 @@
           <t>XV-40203D</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
@@ -84668,8 +85814,10 @@
           <t>XV-40203E</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -84716,8 +85864,10 @@
           <t>XV-40203E</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Control Valve Position Feedback</t>
+        </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
@@ -85564,8 +86714,10 @@
           <t>ES-60202</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -85662,8 +86814,10 @@
           <t>LSL-60201</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -85710,8 +86864,10 @@
           <t>SV-60201</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
@@ -85758,8 +86914,10 @@
           <t>SV-60201</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>0</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -85806,8 +86964,10 @@
           <t>SV-60202</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
@@ -85854,8 +87014,10 @@
           <t>SV-60202</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>0</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -85902,8 +87064,10 @@
           <t>SV-60203</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
@@ -85950,8 +87114,10 @@
           <t>SV-60203</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
-        <v>0</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Process Instrument</t>
+        </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
